--- a/hira_material_automation/output/monthly/202601_202610__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__all_suture_anchor__040021__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:08</t>
+          <t>2026-10-14T23:46:41</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3ce9ed2d53d88fa39c0167c60bc08bffa4e1234df2a4ceefbb9812f33a6e01c8</t>
+          <t>36cb6ab1175ab6dbb797e535d4f724fce690ca7c84fe7c759dc68f8f56a23d95</t>
         </is>
       </c>
     </row>
